--- a/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-magallanes-y-de-la-antartica.xlsx
+++ b/docs/oc-regiones/desarrollo-y-mantencion-de-software-ti-e-iaas/region-de-magallanes-y-de-la-antartica.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1109692-222-CM26</t>
+          <t>1080089-384-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.000.760-9</t>
+          <t>61.607.900-k</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+          <t>APHIX INFORMATICA LIMITADA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>77.754.348-2</t>
+          <t>76.170.582-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,6 +569,250 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
+        <v>14515.89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1609-203-CM25</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>jun-2025</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-06-19</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>72.229.800-4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL XII REGION MAGALLANES Y ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Zecovery Ltda   -    EXEC</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>76.260.080-3</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>30259.78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3637-281-CM25</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>sep-2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>69.251.500-5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN GREGORIO</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SERVICIOS INFORMÁTICOS EN NUBE SPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>77.730.436-4</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>6857.41</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1080089-8982-CM25</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>61.607.900-k</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD MAGALLANES</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>APHIX INFORMATICA LIMITADA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>76.170.582-2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>7039.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1109692-222-CM26</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2239-19-LR23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>62.000.760-9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACION TECNICA ESTATAL DE MAGALLANES Y ANTARTICA CHILENA</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Región de Magallanes y de la Antártica</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SERVICIOS PROFESIONALES INFORMÁTICOS NOBEL TI LIMITADA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>77.754.348-2</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="n">
         <v>9984.700000000001</v>
       </c>
     </row>
